--- a/downloads/Trainory_Risk_Register.xlsx
+++ b/downloads/Trainory_Risk_Register.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="1" r:id="Rca81c1c839d342bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoring Guide" sheetId="2" r:id="R65b4a6579ae94dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Register" sheetId="1" r:id="R02f0b433f4cc4525"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoring Guide" sheetId="2" r:id="R608a1997d4264857"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -86,8 +86,14 @@
       <x:color rgb="FF1F2937"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos Display"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -132,6 +138,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF8D7DA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -241,7 +277,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="104">
+  <x:cellXfs count="111">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -464,6 +500,13 @@
     <x:xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -475,7 +518,7 @@
         <x:color rgb="FF842029"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -486,7 +529,7 @@
         <x:color rgb="FF9A4D00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4C5"/>
         </x:patternFill>
       </x:fill>
@@ -496,7 +539,7 @@
         <x:color rgb="FF7A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -506,7 +549,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -517,7 +560,7 @@
         <x:color rgb="FF842029"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -528,7 +571,7 @@
         <x:color rgb="FF9A4D00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4C5"/>
         </x:patternFill>
       </x:fill>
@@ -538,7 +581,7 @@
         <x:color rgb="FF7A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -548,7 +591,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -559,7 +602,7 @@
         <x:color rgb="FF16324F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE8F0F7"/>
         </x:patternFill>
       </x:fill>
@@ -843,28 +886,68 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>Step 3 | Initial risk identification and qualitative 5 x 5 scoring</x:v>
-      </x:c>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
-      <x:c r="G2" s="5"/>
-      <x:c r="H2" s="5"/>
-      <x:c r="I2" s="5"/>
-      <x:c r="J2" s="5"/>
-      <x:c r="K2" s="5"/>
-      <x:c r="L2" s="5"/>
-      <x:c r="M2" s="5"/>
-      <x:c r="N2" s="5"/>
-      <x:c r="O2" s="5"/>
-      <x:c r="P2" s="5"/>
-      <x:c r="Q2" s="5"/>
-      <x:c r="R2" s="5"/>
-      <x:c r="S2" s="5"/>
-      <x:c r="T2" s="5"/>
-      <x:c r="U2" s="5"/>
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="B2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="C2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="D2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="E2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="F2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="G2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="H2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="I2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="J2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="K2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="L2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="M2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="N2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="O2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="P2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="Q2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="R2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="S2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="T2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
+      <x:c r="U2" s="5" t="str">
+        <x:v>Initial risk identification and qualitative 5 × 5 scoring</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="7" t="str">
@@ -1076,9 +1159,7 @@
       <x:c r="S12" s="46" t="str">
         <x:v>Add customer MFA options, breached-password screening, rate limiting, and stronger alerting.</x:v>
       </x:c>
-      <x:c r="T12" s="46" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T12" s="46"/>
       <x:c r="U12" s="46" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1145,9 +1226,7 @@
       <x:c r="S13" s="47" t="str">
         <x:v>Implement configuration scanning, approved baselines, encryption checks, and recurring cloud reviews.</x:v>
       </x:c>
-      <x:c r="T13" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T13" s="47"/>
       <x:c r="U13" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1214,9 +1293,7 @@
       <x:c r="S14" s="47" t="str">
         <x:v>Create least-privilege roles, quarterly access reviews, privileged-access logs, and approval requirements.</x:v>
       </x:c>
-      <x:c r="T14" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T14" s="47"/>
       <x:c r="U14" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1283,9 +1360,7 @@
       <x:c r="S15" s="47" t="str">
         <x:v>Limit API scopes, protect tokens, validate inputs, monitor failures, and review provider security.</x:v>
       </x:c>
-      <x:c r="T15" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T15" s="47"/>
       <x:c r="U15" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1352,9 +1427,7 @@
       <x:c r="S16" s="47" t="str">
         <x:v>Deploy managed endpoint detection, encryption, patch enforcement, phishing training, and remote wipe.</x:v>
       </x:c>
-      <x:c r="T16" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T16" s="47"/>
       <x:c r="U16" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1421,9 +1494,7 @@
       <x:c r="S17" s="47" t="str">
         <x:v>Add automated dependency, code, and application scanning with severity-based remediation deadlines.</x:v>
       </x:c>
-      <x:c r="T17" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T17" s="47"/>
       <x:c r="U17" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1490,9 +1561,7 @@
       <x:c r="S18" s="47" t="str">
         <x:v>Enable secret scanning, protected branches, least privilege, code-owner approvals, and key rotation procedures.</x:v>
       </x:c>
-      <x:c r="T18" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T18" s="47"/>
       <x:c r="U18" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1559,9 +1628,7 @@
       <x:c r="S19" s="47" t="str">
         <x:v>Require protected approvals, signed artifacts, separated duties, deployment logs, and rollback testing.</x:v>
       </x:c>
-      <x:c r="T19" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T19" s="47"/>
       <x:c r="U19" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1628,9 +1695,7 @@
       <x:c r="S20" s="47" t="str">
         <x:v>Review assurance reports, breach terms, availability commitments, and contingency procedures annually.</x:v>
       </x:c>
-      <x:c r="T20" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T20" s="47"/>
       <x:c r="U20" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1697,9 +1762,7 @@
       <x:c r="S21" s="47" t="str">
         <x:v>Provide recurring phishing training, restrict legacy authentication, add conditional access, and monitor risky sign-ins.</x:v>
       </x:c>
-      <x:c r="T21" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T21" s="47"/>
       <x:c r="U21" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1766,9 +1829,7 @@
       <x:c r="S22" s="47" t="str">
         <x:v>Define recovery objectives, protect backup access, retain isolated copies, and test restoration quarterly.</x:v>
       </x:c>
-      <x:c r="T22" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T22" s="47"/>
       <x:c r="U22" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1835,9 +1896,7 @@
       <x:c r="S23" s="47" t="str">
         <x:v>Centralize critical logs, define alerts, document review responsibilities, and test incident escalation.</x:v>
       </x:c>
-      <x:c r="T23" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T23" s="47"/>
       <x:c r="U23" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1904,9 +1963,7 @@
       <x:c r="S24" s="47" t="str">
         <x:v>Create a data inventory, consent records, retention rules, deletion workflow, and privacy review process.</x:v>
       </x:c>
-      <x:c r="T24" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T24" s="47"/>
       <x:c r="U24" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -1973,9 +2030,7 @@
       <x:c r="S25" s="47" t="str">
         <x:v>Use an offboarding checklist, centralized account inventory, immediate disablement, and completion evidence.</x:v>
       </x:c>
-      <x:c r="T25" s="47" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T25" s="47"/>
       <x:c r="U25" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -2042,9 +2097,7 @@
       <x:c r="S26" s="48" t="str">
         <x:v>Define uptime targets, add rate limiting and scaling alerts, test failover, and document customer communications.</x:v>
       </x:c>
-      <x:c r="T26" s="48" t="str">
-        <x:v>Fictional assessment assumption; validate with asset and process owners.</x:v>
-      </x:c>
+      <x:c r="T26" s="48"/>
       <x:c r="U26" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
@@ -2095,7 +2148,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f62240d783c4b80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8666126c229e45d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2111,14 +2164,22 @@
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="2" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="110" t="str">
         <x:v>Trainory Risk Scoring Guide</x:v>
       </x:c>
-      <x:c r="B1" s="2"/>
-      <x:c r="C1" s="2"/>
-      <x:c r="D1" s="2"/>
-      <x:c r="E1" s="2"/>
+      <x:c r="B1" s="110" t="str">
+        <x:v>Trainory Risk Scoring Guide</x:v>
+      </x:c>
+      <x:c r="C1" s="110" t="str">
+        <x:v>Trainory Risk Scoring Guide</x:v>
+      </x:c>
+      <x:c r="D1" s="110" t="str">
+        <x:v>Trainory Risk Scoring Guide</x:v>
+      </x:c>
+      <x:c r="E1" s="110" t="str">
+        <x:v>Trainory Risk Scoring Guide</x:v>
+      </x:c>
       <x:c r="F1" s="2"/>
     </x:row>
     <x:row r="3">
@@ -2212,9 +2273,7 @@
       <x:c r="B10" s="7" t="str">
         <x:v>Rating</x:v>
       </x:c>
-      <x:c r="D10" s="76" t="str">
-        <x:v>How to explain this in an interview</x:v>
-      </x:c>
+      <x:c r="D10" s="76"/>
       <x:c r="E10" s="76"/>
       <x:c r="F10" s="76"/>
     </x:row>
@@ -2225,9 +2284,7 @@
       <x:c r="B11" s="72" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="D11" s="95" t="str">
-        <x:v>I identified credible threat scenarios connected to Trainory's assets. I scored likelihood and impact before considering controls to determine inherent risk. I then considered the assumed effectiveness of existing controls and calculated residual risk. Finally, I assigned an owner, treatment, target date, and recommended actions so the register supports decisions rather than merely listing problems.</x:v>
-      </x:c>
+      <x:c r="D11" s="95"/>
       <x:c r="E11" s="96"/>
       <x:c r="F11" s="97"/>
     </x:row>
@@ -2271,9 +2328,9 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="D10:F10"/>
     <x:mergeCell ref="D11:F15"/>
+    <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
